--- a/artfynd/A 7316-2025 artfynd.xlsx
+++ b/artfynd/A 7316-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69231693</v>
+        <v>69231699</v>
       </c>
       <c r="B2" t="n">
-        <v>57010</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102124</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578831.9399108647</v>
+        <v>578832</v>
       </c>
       <c r="R2" t="n">
-        <v>6495330.563690147</v>
+        <v>6495331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,6 +786,243 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69231693</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58607</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102124</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vinterhämpling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Linaria flavirostris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Drögestad, Svensksundsviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>578832</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6495331</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dagsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-01-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-01-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrik Lindmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrik Lindmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>65657268</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57572</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205660</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Silltrut</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Larus fuscus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Drögestad, Svensksundsviken, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578832</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6495331</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dagsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-05-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-05-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På fältet intill gården med gråtrutar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7316-2025 artfynd.xlsx
+++ b/artfynd/A 7316-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69231699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69231693</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,8 +1038,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65657268</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>